--- a/analysis_outputs/step_00/Step0_Workbook_Audit.xlsx
+++ b/analysis_outputs/step_00/Step0_Workbook_Audit.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
